--- a/Data/EC/NIT-9002028561.xlsx
+++ b/Data/EC/NIT-9002028561.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88240235-722E-455E-8181-2A9B2FBF7D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B13470DF-E4FC-43B0-9309-970F9B4984E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{70D833C3-E09C-4071-A551-B6033234CA4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D2DCEA6A-8652-44BB-801D-8DB686F14675}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,103 +71,103 @@
     <t>LUIS MANUEL CAICEDO LOPEZ</t>
   </si>
   <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
-  </si>
-  <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -266,9 +266,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -281,7 +279,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -481,23 +481,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -525,10 +525,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,22 +566,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE7AC530-47C4-1965-C34B-0BB5C7B37BD8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4117CC77-43B1-6BA4-0C10-A99075FBBE1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -603,7 +603,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -932,23 +932,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474BEA08-6C42-4D7F-BBD7-CB5F8964CC45}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0584DDD2-1820-4DAB-800C-79502EDB5243}">
   <dimension ref="B2:J54"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -961,7 +961,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -972,7 +972,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -983,7 +983,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -994,8 +994,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
@@ -1010,8 +1010,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1026,8 +1026,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>46</v>
       </c>
@@ -1042,8 +1042,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>47</v>
       </c>
@@ -1062,7 +1062,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>24640</v>
+        <v>20533</v>
       </c>
       <c r="G16" s="18">
         <v>616000</v>
@@ -1114,7 +1114,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1137,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1160,7 +1160,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1183,7 +1183,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1206,7 +1206,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1229,7 +1229,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1252,7 +1252,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1275,7 +1275,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1298,7 +1298,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1321,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1344,7 +1344,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1367,7 +1367,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1390,7 +1390,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1413,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1436,7 +1436,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1459,7 +1459,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1482,7 +1482,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1551,7 +1551,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1574,7 +1574,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1597,7 +1597,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1620,7 +1620,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1643,7 +1643,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1666,7 +1666,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1689,7 +1689,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1712,7 +1712,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1735,7 +1735,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1758,7 +1758,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1781,7 +1781,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +1804,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1827,7 +1827,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="21" t="s">
         <v>8</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>43</v>
       </c>
       <c r="F48" s="24">
-        <v>20533</v>
+        <v>24640</v>
       </c>
       <c r="G48" s="24">
         <v>616000</v>
@@ -1850,7 +1850,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="26"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="32" t="s">
         <v>53</v>
       </c>
@@ -1861,7 +1861,7 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="32" t="s">
         <v>52</v>
       </c>
